--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 25.12.2025 a 31.12.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 25.12.2025 a 31.12.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/E-MAILS Santander Recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCC8211A-35F3-46FC-80DB-ABE07890DAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2251E8DC-2774-4975-95C9-D02868F364A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="25.12" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="133">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -143,6 +143,366 @@
 oposta em questão se encontra em duplicidade com a apólice 5177202
 42E312540879, para prosseguirmos com a emissão se faz necessário r
 ealizar o cancelamento da mesma. </t>
+  </si>
+  <si>
+    <t>LIMBO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RITA DE CASSIA SARVANINI MATHIAS  cpf 9004186808 </t>
+  </si>
+  <si>
+    <t>Demais Motivos</t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 24.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLODOALDO LEITE MARTINS                      </t>
+  </si>
+  <si>
+    <t>Desistência;</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 24.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS PACHU FREITAS                          </t>
+  </si>
+  <si>
+    <t>Falta de Vistoria;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de vistoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUGLAS GAMA DE SA                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO JOSE LEITE FARIAS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTOVAO RODRIGUES DA SILVA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GT PRODUCOES E REPRESENTACOES LTDA EPP       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERAX SERVICOS E TELECOMUNICACAO LTDA EPP    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO CARLOS DO NASCIMENTO               </t>
+  </si>
+  <si>
+    <t>Vistoria Frustrada;</t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDSON VANDERLEI SAVIAN                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIANE BITENCOURT DE OLIVEIRA               </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO: Traseira e lateral do motorista placa obstruída , Chassi local errado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFFERSON SANTOS DA COSTA                    </t>
+  </si>
+  <si>
+    <t>Conclusão: FRUSTADO/ RECUSA: CLIENTE NÃO CONCLUIU A FOTO DENTRO DO PRAZO/ FOTOS INCORRETAS: Painel com carro ligado, Chassi, Frente e lateral do motorista.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO PEDRO MAFORT DINIZ MONTEIRO             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAYSSA DA SILVA CORREIA                      </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do pass, Frente e lateral do mot, Traseira e lateral do mot, Traseira e lateral do pass,Motor e placa, Painel, Chassi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIANA MAROSTEGA FAGUNDES                   </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI (LOCAL INCORRETO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE NILTON AGUIAR SANTOS                    </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSELI NASCIMENTO ALBUQUERQUE                </t>
+  </si>
+  <si>
+    <t>FRUSTRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA PEREIRA DE OLIVEIRA                   </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro, Traseira e lateral do motorista, Frente e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERACILDE GONCALVES DINATE                    </t>
+  </si>
+  <si>
+    <t>Vistoria Recusada</t>
+  </si>
+  <si>
+    <t>Bloqueio recusado devido ao parecer da vistoria prévia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALINE LAYOLA PUCCIARELLIS MARTINS SANTOS     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDIR DA SILVA LOPES                        </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO, FOTO DO CRLV NÃO APRESENTADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVANA APARECIDA BALLINI                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE CARNEIRO ROCHA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA ALICE DE CARVALHO                        </t>
+  </si>
+  <si>
+    <t>Veículo informado é diferente do calculado&lt;br&gt;&lt;b
+r&gt;Constatamos que o modelo do veículo informado na cotação difere
+do constado, segue abaixo informação retornada pelo sistema atravé
+s do chassi do veículo: &lt;br&gt;&lt;br&gt;Modelo constatado: FIAT PALIO EX
+1.0MPI GAS 2P&lt;br&gt;FIPE: 001004-9&lt;br&gt;Valor do prêmio: 10x R$ 238,38
+&lt;br&gt;Franquia: R$ 1.183,00&lt;br&gt;&lt;br&gt;Podemos emitir desse forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL BARBOSA DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA BEATRIZ VIANNA TEIXEIRA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS MARTINS DA COSTA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ADRIANO LIMA DA SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDSON SEIZO MORI                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Nup- Cancelamento 24.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CESAR AUGUSTO DOS SANTOS CHAIM               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA ELISA FROZINO COUTINHO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIZAUTO DA SILVA MEDEIROS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANOEL GOMES DE MOURA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIANO MATTOS DE SOUZA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROWSTEK CONSTRUCOES ELETRICA LTDA EPP        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIGUEL AUGUSTO DA SILVA AMERICO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA IZILDA PREVIATO SIMOES                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANUZIA FERNANDES DA SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABLIO KIOMA DA SILVA FREITAS                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL SILVA BARRETO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLAVIO ESTEVAM DE OLIVEIRA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERICLES LIMA DE SOUSA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ GUSTAVO VIEIRA ROMUALDO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATIANE FRANKLIN GERALDO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERALDO RAMOS OLIVEIRA DA SILVA              </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAIRO ALVES COSTA                            </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2025 a 2026.&lt;br&gt; Endosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JENNIFER FORELL DANNUS                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE MARCELO GRAEBIN                    </t>
+  </si>
+  <si>
+    <t>Necessário que seja enviado a cópia da apólice, pois a central de
+bônus não está identificando a CI do endosso apresentado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIO RICCI NETO                             </t>
+  </si>
+  <si>
+    <t>Confirmar bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA PAULA FORTUNATO DA COSTA                 </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve sinistro na apólice anterior, portanto a renovaçã
+o correta é externa com sinistro, conforme regra diminui uma class
+e de bônus, assim sendo o correto bônus 9. &lt;br&gt;Com a correção fico
+u 10x R$ 416,65. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CESARIO MORITA                               </t>
+  </si>
+  <si>
+    <t>Co
+nforme regra, apólice não completou 365 dias vigente , portanto de
+ve-se manter a classe de bônus, assim sendo o bônus correto 4.&lt;br&gt;
+Com a correção ficou 10x R$ 384,37. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS FERNANDO OURA HONORIO MARQUES           </t>
+  </si>
+  <si>
+    <t>Não foi possível seguir com o ajuste devido duplicidade com a prop
+osta 135833489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVO CERAMICA LTDA ME                        </t>
+  </si>
+  <si>
+    <t>C
+onforme regra de apólices canceladas por vigência de curto prazo,
+houve quebra de vigência de 326 dias, portanto deve-se reduzir 10
+classes de bônus, assim sendo o correto bônus 0.&lt;br&gt;Com a correçã
+o ficou 10x R$ 365,78. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELLO CHAVES ROSA                         </t>
+  </si>
+  <si>
+    <t>Aceitação condicionada à confirmação de bônus na CBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANTE MOREIRA FILHO                          </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve sinistro na apólice anterior, portanto a renovaçã
+o correta é externa com sinistro, conforme regra diminui uma class
+e de bônus, assim sendo o correto bônus 9. &lt;br&gt;Com a correção fico
+u 10x R$ 343,64. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELCIA RITA PIRONDI CAIRES                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIELA CAMPANA GATTO                        </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2025 a 2026.&lt;br&gt; Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAMILLY NICACIO NICOLETE                     </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve sinistro na apólice anterior, portanto a renovaçã
+o correta é externa com sinistro, conforme regra diminui uma class
+e de bônus, assim sendo o correto bônus 0. &lt;br&gt;Com a correção fico
+u 10x R$ 318,78. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAIMUNDO INACIO DOS SANTOS                   </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice anterior 2024/2025 ou CI atual .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEBORA DOS SANTOS                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veículo em duplicidade </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANA OLIVEIRA PEREIRA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATIANA IRMANN BERNARDI                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALINEIA DA SILVA CAMPOS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposta em duplicidade&lt;br&gt;&lt;br&gt;Informamos que a p
+roposta em questão se encontra em duplicidade com a apólice 517720
+2521312735718, para prosseguirmos com a emissão se faz necessário
+realizar o cancelamento dela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNH COMPOSITOS E MODELAGEM LTDA ME           </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que
+a apólice consta ativa na congênere, para que possamos prossegui
+r coma liberação do bloqueio será necessário a apresentação do e
+ndosso de cancelamento emitido, a atualização junto a Central de B
+ônus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICARDO PEREIRA DO NASCIMENTO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIO LUIZ RIBEIRO SOBRAL                    </t>
   </si>
 </sst>
 </file>
@@ -379,39 +739,6 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -422,12 +749,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -479,14 +839,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -583,58 +937,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1024,25 +1361,25 @@
       <c r="B2" s="7">
         <v>46011</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="23">
         <v>46016</v>
       </c>
-      <c r="D2" s="74">
+      <c r="D2" s="21">
         <v>135784618</v>
       </c>
       <c r="E2" s="17">
         <v>3450178644</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="73" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="76" t="s">
+      <c r="H2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="44">
+      <c r="I2" s="42">
         <v>46007</v>
       </c>
     </row>
@@ -1053,25 +1390,25 @@
       <c r="B3" s="7">
         <v>46014</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="23">
         <v>46016</v>
       </c>
-      <c r="D3" s="74">
+      <c r="D3" s="21">
         <v>135800415</v>
       </c>
       <c r="E3" s="17">
         <v>3450179953</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="44">
+      <c r="I3" s="42">
         <v>46007</v>
       </c>
     </row>
@@ -1082,25 +1419,25 @@
       <c r="B4" s="7">
         <v>46000</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="23">
         <v>46016</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D4" s="21">
         <v>135834039</v>
       </c>
       <c r="E4" s="17">
         <v>3450177775</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="76" t="s">
+      <c r="H4" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="42">
         <v>46010</v>
       </c>
     </row>
@@ -1111,25 +1448,25 @@
       <c r="B5" s="7">
         <v>46020</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="23">
         <v>46016</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D5" s="21">
         <v>135830606</v>
       </c>
       <c r="E5" s="17">
         <v>3450178171</v>
       </c>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="73" t="s">
+      <c r="G5" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="76" t="s">
+      <c r="H5" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="42">
         <v>46010</v>
       </c>
     </row>
@@ -1140,25 +1477,25 @@
       <c r="B6" s="7">
         <v>46029</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="23">
         <v>46016</v>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="21">
         <v>135824642</v>
       </c>
       <c r="E6" s="17">
         <v>3450176356</v>
       </c>
-      <c r="F6" s="72" t="s">
+      <c r="F6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="73" t="s">
+      <c r="G6" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="76" t="s">
+      <c r="H6" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="42">
         <v>46010</v>
       </c>
     </row>
@@ -1169,25 +1506,25 @@
       <c r="B7" s="7">
         <v>46000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="23">
         <v>46016</v>
       </c>
-      <c r="D7" s="74">
+      <c r="D7" s="21">
         <v>135833835</v>
       </c>
       <c r="E7" s="17">
         <v>3450177830</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="F7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="73" t="s">
+      <c r="G7" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="76" t="s">
+      <c r="H7" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="42">
         <v>46010</v>
       </c>
     </row>
@@ -1198,25 +1535,25 @@
       <c r="B8" s="7">
         <v>45999</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="23">
         <v>46016</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="21">
         <v>135824707</v>
       </c>
       <c r="E8" s="17">
         <v>3450176235</v>
       </c>
-      <c r="F8" s="72" t="s">
+      <c r="F8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="73" t="s">
+      <c r="G8" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="76" t="s">
+      <c r="H8" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="42">
         <v>46010</v>
       </c>
     </row>
@@ -1227,25 +1564,25 @@
       <c r="B9" s="7">
         <v>46003</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="23">
         <v>46016</v>
       </c>
-      <c r="D9" s="74">
+      <c r="D9" s="21">
         <v>135835104</v>
       </c>
       <c r="E9" s="17">
         <v>3450183055</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="73" t="s">
+      <c r="G9" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="76" t="s">
+      <c r="H9" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="42">
         <v>46014</v>
       </c>
     </row>
@@ -1256,25 +1593,25 @@
       <c r="B10" s="7">
         <v>46004</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="23">
         <v>46016</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="21">
         <v>135826631</v>
       </c>
       <c r="E10" s="17">
         <v>3450182263</v>
       </c>
-      <c r="F10" s="72" t="s">
+      <c r="F10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="76" t="s">
+      <c r="H10" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="42">
         <v>46014</v>
       </c>
     </row>
@@ -1285,25 +1622,25 @@
       <c r="B11" s="7">
         <v>46003</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="23">
         <v>46016</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="21">
         <v>135839826</v>
       </c>
       <c r="E11" s="17">
         <v>3450183572</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="73" t="s">
+      <c r="G11" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="76" t="s">
+      <c r="H11" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="42">
         <v>46014</v>
       </c>
     </row>
@@ -1314,236 +1651,236 @@
       <c r="B12" s="7">
         <v>46003</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="23">
         <v>46016</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="62">
         <v>135843387</v>
       </c>
-      <c r="E12" s="57">
+      <c r="E12" s="55">
         <v>3450184034</v>
       </c>
-      <c r="F12" s="71" t="s">
+      <c r="F12" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="42" t="s">
+      <c r="G12" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="76" t="s">
+      <c r="H12" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="42">
         <v>46014</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="43"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="41"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="44"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="43"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="41"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="44"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="42"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6"/>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="43"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="41"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="44"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="42"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="43"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="41"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="44"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="42"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="43"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="41"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="44"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="42"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
-      <c r="B18" s="47"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="43"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="41"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="44"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="42"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="43"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="41"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
+      <c r="G19" s="40"/>
       <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="I19" s="42"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="43"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="41"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
+      <c r="G20" s="40"/>
       <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="43"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="41"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
+      <c r="G21" s="40"/>
       <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="43"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="41"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
+      <c r="G22" s="40"/>
       <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="43"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="41"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
+      <c r="G23" s="40"/>
       <c r="H23" s="12"/>
-      <c r="I23" s="44"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="43"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="41"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
+      <c r="G24" s="40"/>
       <c r="H24" s="12"/>
-      <c r="I24" s="44"/>
+      <c r="I24" s="42"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="43"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="41"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
+      <c r="G25" s="40"/>
       <c r="H25" s="12"/>
-      <c r="I25" s="44"/>
+      <c r="I25" s="42"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="43"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="41"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
+      <c r="G26" s="40"/>
       <c r="H26" s="12"/>
-      <c r="I26" s="44"/>
+      <c r="I26" s="42"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="43"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="41"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
+      <c r="G27" s="40"/>
       <c r="H27" s="12"/>
-      <c r="I27" s="44"/>
+      <c r="I27" s="42"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="43"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="41"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
+      <c r="G28" s="40"/>
       <c r="H28" s="12"/>
-      <c r="I28" s="44"/>
+      <c r="I28" s="42"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="43"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="41"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
+      <c r="G29" s="40"/>
       <c r="H29" s="12"/>
-      <c r="I29" s="44"/>
+      <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="43"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="41"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
+      <c r="G30" s="40"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="I30" s="42"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="43"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
+      <c r="G31" s="40"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="49"/>
+      <c r="I31" s="47"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -1553,7 +1890,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="48"/>
+      <c r="H32" s="46"/>
       <c r="I32" s="12"/>
     </row>
   </sheetData>
@@ -1563,7 +1900,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F12">
-    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A31" xr:uid="{9AD193C7-0C28-47DE-BB22-7B92526E3023}">
@@ -1579,481 +1916,1374 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" style="16" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" customWidth="1"/>
+    <col min="6" max="6" width="51.140625" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" customWidth="1"/>
+    <col min="8" max="8" width="33.7109375" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="49" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="55">
+      <c r="A2" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="53">
         <v>46007</v>
       </c>
-      <c r="C2" s="56">
+      <c r="C2" s="54">
         <v>46015</v>
       </c>
-      <c r="D2" s="60"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="59"/>
+      <c r="D2" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450188049</v>
+      </c>
+      <c r="F2" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="57"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="44"/>
+      <c r="A3" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="53">
+        <v>46011</v>
+      </c>
+      <c r="C3" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D3" s="65">
+        <v>135836003</v>
+      </c>
+      <c r="E3" s="66">
+        <v>3450183154</v>
+      </c>
+      <c r="F3" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="57">
+        <v>46015</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="44"/>
+      <c r="A4" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="53">
+        <v>46006</v>
+      </c>
+      <c r="C4" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D4" s="65">
+        <v>135862723</v>
+      </c>
+      <c r="E4" s="66">
+        <v>3450185453</v>
+      </c>
+      <c r="F4" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="57">
+        <v>46006</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="44"/>
+      <c r="A5" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="53">
+        <v>46007</v>
+      </c>
+      <c r="C5" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D5" s="65">
+        <v>135881310</v>
+      </c>
+      <c r="E5" s="66">
+        <v>3450186840</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="57">
+        <v>46007</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="A6" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="53">
+        <v>46006</v>
+      </c>
+      <c r="C6" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D6" s="65">
+        <v>135894661</v>
+      </c>
+      <c r="E6" s="66">
+        <v>3450184540</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="57">
+        <v>46015</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="44"/>
+      <c r="A7" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="53">
+        <v>46007</v>
+      </c>
+      <c r="C7" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D7" s="65">
+        <v>135890943</v>
+      </c>
+      <c r="E7" s="66">
+        <v>3450187697</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="57">
+        <v>46007</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="44"/>
+      <c r="A8" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="53">
+        <v>46003</v>
+      </c>
+      <c r="C8" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D8" s="65">
+        <v>135894746</v>
+      </c>
+      <c r="E8" s="66">
+        <v>3450184045</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="57">
+        <v>46003</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="44"/>
+      <c r="A9" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="53">
+        <v>46007</v>
+      </c>
+      <c r="C9" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D9" s="65">
+        <v>135890905</v>
+      </c>
+      <c r="E9" s="66">
+        <v>3450187686</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="57">
+        <v>46007</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="A10" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="53">
+        <v>46009</v>
+      </c>
+      <c r="C10" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D10" s="65">
+        <v>135926129</v>
+      </c>
+      <c r="E10" s="66">
+        <v>3450190580</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="57">
+        <v>46009</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="A11" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="53">
+        <v>46013</v>
+      </c>
+      <c r="C11" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D11" s="65">
+        <v>135931101</v>
+      </c>
+      <c r="E11" s="66">
+        <v>3450190986</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="57">
+        <v>46015</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="A12" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="53">
+        <v>46009</v>
+      </c>
+      <c r="C12" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D12" s="65">
+        <v>135934684</v>
+      </c>
+      <c r="E12" s="66">
+        <v>3450191382</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="57">
+        <v>46009</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="A13" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="53">
+        <v>46010</v>
+      </c>
+      <c r="C13" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D13" s="65">
+        <v>135946093</v>
+      </c>
+      <c r="E13" s="66">
+        <v>3450192075</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="57">
+        <v>46010</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="A14" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="53">
+        <v>46010</v>
+      </c>
+      <c r="C14" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D14" s="65">
+        <v>135947426</v>
+      </c>
+      <c r="E14" s="66">
+        <v>3450192163</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="57">
+        <v>46015</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="A15" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="53">
+        <v>46010</v>
+      </c>
+      <c r="C15" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D15" s="65">
+        <v>135957031</v>
+      </c>
+      <c r="E15" s="66">
+        <v>3450192878</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="57">
+        <v>46010</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="A16" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="53">
+        <v>46010</v>
+      </c>
+      <c r="C16" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D16" s="65">
+        <v>135959927</v>
+      </c>
+      <c r="E16" s="66">
+        <v>3450193175</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="57">
+        <v>46010</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="A17" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="53">
+        <v>46010</v>
+      </c>
+      <c r="C17" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D17" s="65">
+        <v>135962512</v>
+      </c>
+      <c r="E17" s="66">
+        <v>3450193472</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" s="57">
+        <v>46010</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="A18" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="53">
+        <v>46010</v>
+      </c>
+      <c r="C18" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D18" s="65">
+        <v>135943050</v>
+      </c>
+      <c r="E18" s="66">
+        <v>3450191844</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="57">
+        <v>46010</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="A19" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="53">
+        <v>46011</v>
+      </c>
+      <c r="C19" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D19" s="65">
+        <v>135965183</v>
+      </c>
+      <c r="E19" s="66">
+        <v>3450193659</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I19" s="57">
+        <v>46011</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="A20" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="53">
+        <v>46013</v>
+      </c>
+      <c r="C20" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D20" s="65">
+        <v>135981139</v>
+      </c>
+      <c r="E20" s="66">
+        <v>3450194726</v>
+      </c>
+      <c r="F20" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" s="57">
+        <v>46013</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="A21" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="53">
+        <v>46008</v>
+      </c>
+      <c r="C21" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D21" s="65">
+        <v>135999500</v>
+      </c>
+      <c r="E21" s="66">
+        <v>3450188160</v>
+      </c>
+      <c r="F21" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="57">
+        <v>46015</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="7">
+        <v>46010</v>
+      </c>
+      <c r="C22" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D22" s="65">
+        <v>135948847</v>
+      </c>
+      <c r="E22" s="66">
+        <v>3450192273</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="42">
+        <v>46010</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="44"/>
+      <c r="B23" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C23" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D23" s="65">
+        <v>135867298</v>
+      </c>
+      <c r="E23" s="66">
+        <v>3450185893</v>
+      </c>
+      <c r="F23" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="42">
+        <v>46006</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="44"/>
+      <c r="B24" s="7">
+        <v>46014</v>
+      </c>
+      <c r="C24" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D24" s="65">
+        <v>135997309</v>
+      </c>
+      <c r="E24" s="66">
+        <v>3450195420</v>
+      </c>
+      <c r="F24" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="42">
+        <v>46015</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="44"/>
+      <c r="B25" s="7">
+        <v>46007</v>
+      </c>
+      <c r="C25" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D25" s="65">
+        <v>135889906</v>
+      </c>
+      <c r="E25" s="66">
+        <v>3450187587</v>
+      </c>
+      <c r="F25" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25" s="42">
+        <v>46010</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="44"/>
+      <c r="B26" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C26" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D26" s="65">
+        <v>136014551</v>
+      </c>
+      <c r="E26" s="66">
+        <v>3450197212</v>
+      </c>
+      <c r="F26" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I26" s="42">
+        <v>46015</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="44"/>
+      <c r="B27" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C27" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D27" s="65">
+        <v>135862967</v>
+      </c>
+      <c r="E27" s="66">
+        <v>3450185497</v>
+      </c>
+      <c r="F27" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="42">
+        <v>46015</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="44"/>
+      <c r="B28" s="7">
+        <v>46033</v>
+      </c>
+      <c r="C28" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D28" s="65">
+        <v>135904895</v>
+      </c>
+      <c r="E28" s="66">
+        <v>3450188918</v>
+      </c>
+      <c r="F28" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28" s="42">
+        <v>46015</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="44"/>
+      <c r="B29" s="7">
+        <v>46003</v>
+      </c>
+      <c r="C29" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D29" s="65">
+        <v>135894780</v>
+      </c>
+      <c r="E29" s="66">
+        <v>3450183792</v>
+      </c>
+      <c r="F29" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29" s="42">
+        <v>46015</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="B30" s="7">
+        <v>46008</v>
+      </c>
+      <c r="C30" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D30" s="65">
+        <v>135905418</v>
+      </c>
+      <c r="E30" s="66">
+        <v>3450188984</v>
+      </c>
+      <c r="F30" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="42">
+        <v>46015</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="B31" s="7">
+        <v>46005</v>
+      </c>
+      <c r="C31" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D31" s="65">
+        <v>135850238</v>
+      </c>
+      <c r="E31" s="66">
+        <v>3450184485</v>
+      </c>
+      <c r="F31" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="G31" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I31" s="42">
+        <v>46005</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
+      <c r="B32" s="7">
+        <v>46005</v>
+      </c>
+      <c r="C32" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D32" s="65">
+        <v>135850447</v>
+      </c>
+      <c r="E32" s="66">
+        <v>3450184507</v>
+      </c>
+      <c r="F32" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I32" s="42">
+        <v>46005</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="24"/>
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C33" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D33" s="65">
+        <v>135856612</v>
+      </c>
+      <c r="E33" s="66">
+        <v>3450184914</v>
+      </c>
+      <c r="F33" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="G33" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I33" s="42">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C34" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D34" s="65">
+        <v>135858579</v>
+      </c>
+      <c r="E34" s="66">
+        <v>3450180085</v>
+      </c>
+      <c r="F34" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I34" s="42">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C35" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D35" s="65">
+        <v>135858945</v>
+      </c>
+      <c r="E35" s="66">
+        <v>3450185167</v>
+      </c>
+      <c r="F35" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="G35" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I35" s="42">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C36" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D36" s="65">
+        <v>135860950</v>
+      </c>
+      <c r="E36" s="66">
+        <v>3450180063</v>
+      </c>
+      <c r="F36" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="G36" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I36" s="42">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C37" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D37" s="65">
+        <v>135869585</v>
+      </c>
+      <c r="E37" s="66">
+        <v>3450186146</v>
+      </c>
+      <c r="F37" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I37" s="42">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C38" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D38" s="65">
+        <v>135870412</v>
+      </c>
+      <c r="E38" s="66">
+        <v>3450186234</v>
+      </c>
+      <c r="F38" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="G38" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I38" s="42">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C39" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D39" s="65">
+        <v>135871053</v>
+      </c>
+      <c r="E39" s="66">
+        <v>3450180074</v>
+      </c>
+      <c r="F39" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="42">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C40" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D40" s="65">
+        <v>135871182</v>
+      </c>
+      <c r="E40" s="66">
+        <v>3450180052</v>
+      </c>
+      <c r="F40" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="G40" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I40" s="42">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C41" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D41" s="65">
+        <v>135871644</v>
+      </c>
+      <c r="E41" s="66">
+        <v>3450178985</v>
+      </c>
+      <c r="F41" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I41" s="42">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="7">
+        <v>46007</v>
+      </c>
+      <c r="C42" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D42" s="65">
+        <v>135882829</v>
+      </c>
+      <c r="E42" s="66">
+        <v>3450186950</v>
+      </c>
+      <c r="F42" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="G42" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I42" s="42">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="7">
+        <v>46007</v>
+      </c>
+      <c r="C43" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D43" s="65">
+        <v>135882939</v>
+      </c>
+      <c r="E43" s="66">
+        <v>3450186982</v>
+      </c>
+      <c r="F43" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="G43" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I43" s="42">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C44" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D44" s="65">
+        <v>135893655</v>
+      </c>
+      <c r="E44" s="66">
+        <v>3450182098</v>
+      </c>
+      <c r="F44" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="G44" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I44" s="42">
+        <v>46002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C45" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D45" s="65">
+        <v>135894568</v>
+      </c>
+      <c r="E45" s="66">
+        <v>3450180756</v>
+      </c>
+      <c r="F45" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="G45" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I45" s="42">
+        <v>46002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="7">
+        <v>46003</v>
+      </c>
+      <c r="C46" s="54">
+        <v>46017</v>
+      </c>
+      <c r="D46" s="65">
+        <v>135894812</v>
+      </c>
+      <c r="E46" s="66">
+        <v>3450183671</v>
+      </c>
+      <c r="F46" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="G46" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I46" s="42">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="6"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="42"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:F32">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A47" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G47" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2063,7 +3293,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.85546875" style="16" customWidth="1"/>
@@ -2073,7 +3303,7 @@
     <col min="6" max="6" width="30.140625" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="24" customWidth="1"/>
+    <col min="9" max="9" width="21" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2101,7 +3331,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2109,472 +3339,694 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="44"/>
+      <c r="B2" s="69">
+        <v>46003</v>
+      </c>
+      <c r="C2" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D2" s="65">
+        <v>135839979</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450183594</v>
+      </c>
+      <c r="F2" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="42">
+        <v>46014</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="69">
+        <v>46003</v>
+      </c>
+      <c r="C3" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D3" s="65">
+        <v>135842234</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450183880</v>
+      </c>
+      <c r="F3" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="71" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="42">
+        <v>46014</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="69">
+        <v>46003</v>
+      </c>
+      <c r="C4" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D4" s="65">
+        <v>135831039</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450182659</v>
+      </c>
+      <c r="F4" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="42">
+        <v>46014</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="49"/>
+      <c r="B5" s="69">
+        <v>46031</v>
+      </c>
+      <c r="C5" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D5" s="65">
+        <v>135894528</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450180965</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="71" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="42">
+        <v>46017</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="69">
+        <v>46002</v>
+      </c>
+      <c r="C6" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D6" s="65">
+        <v>135894612</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450180393</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I6" s="42">
+        <v>46018</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="69">
+        <v>46022</v>
+      </c>
+      <c r="C7" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D7" s="65">
+        <v>135844432</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450184144</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="42">
+        <v>46014</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="69">
+        <v>46033</v>
+      </c>
+      <c r="C8" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D8" s="65">
+        <v>135830974</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450182648</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="42">
+        <v>46014</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="69">
+        <v>46020</v>
+      </c>
+      <c r="C9" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D9" s="65">
+        <v>135833489</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450182901</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="42">
+        <v>46017</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="69">
+        <v>46004</v>
+      </c>
+      <c r="C10" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D10" s="65">
+        <v>135847358</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450184430</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="I10" s="42">
+        <v>46014</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="69">
+        <v>46013</v>
+      </c>
+      <c r="C11" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D11" s="65">
+        <v>135850413</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450184496</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="I11" s="42">
+        <v>46005</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="69">
+        <v>46005</v>
+      </c>
+      <c r="C12" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D12" s="65">
+        <v>135838942</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450183430</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="I12" s="42">
+        <v>46005</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="69">
+        <v>46006</v>
+      </c>
+      <c r="C13" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D13" s="65">
+        <v>135841301</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450183737</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" s="42">
+        <v>46014</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="B14" s="69">
+        <v>46021</v>
+      </c>
+      <c r="C14" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D14" s="65">
+        <v>135842472</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450183902</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="G14" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="I14" s="42">
+        <v>46014</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="69">
+        <v>46003</v>
+      </c>
+      <c r="C15" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D15" s="65">
+        <v>135845145</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450184254</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="42">
+        <v>46014</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="69">
+        <v>46005</v>
+      </c>
+      <c r="C16" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D16" s="65">
+        <v>135845723</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450184320</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="I16" s="42">
+        <v>46014</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="69">
+        <v>46008</v>
+      </c>
+      <c r="C17" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D17" s="65">
+        <v>135850663</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450184530</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="I17" s="42">
+        <v>46018</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="69">
+        <v>46000</v>
+      </c>
+      <c r="C18" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D18" s="65">
+        <v>135856766</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450177423</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="I18" s="42">
+        <v>46017</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="69">
+        <v>46006</v>
+      </c>
+      <c r="C19" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D19" s="65">
+        <v>135867779</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450185959</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="I19" s="42">
+        <v>46018</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="B20" s="69">
+        <v>46006</v>
+      </c>
+      <c r="C20" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D20" s="65">
+        <v>135866951</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450185871</v>
+      </c>
+      <c r="F20" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="42">
+        <v>46009</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="B21" s="69">
+        <v>46007</v>
+      </c>
+      <c r="C21" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D21" s="65">
+        <v>135889937</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450187609</v>
+      </c>
+      <c r="F21" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="71" t="s">
+        <v>130</v>
+      </c>
+      <c r="I21" s="42">
+        <v>46009</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="69">
+        <v>46007</v>
+      </c>
+      <c r="C22" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D22" s="65">
+        <v>135890169</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450187620</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="70" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" s="42">
+        <v>46009</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="69">
+        <v>46003</v>
+      </c>
+      <c r="C23" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D23" s="65">
+        <v>135894682</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450184420</v>
+      </c>
+      <c r="F23" s="63" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="42">
+        <v>46010</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="69">
+        <v>46012</v>
+      </c>
+      <c r="C24" s="42">
+        <v>46018</v>
+      </c>
+      <c r="D24" s="65">
+        <v>135894739</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450184090</v>
+      </c>
+      <c r="F24" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="42">
+        <v>46010</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="17"/>
       <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="42"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A33" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
-      <formula1>#REF!</formula1>
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B24" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A24" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+      <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G24" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
-      <formula1>$J$2</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2629,40 +4081,40 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24"/>
       <c r="E2" s="8"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="27"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24"/>
       <c r="E3" s="8"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="27"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="24"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24"/>
       <c r="E4" s="8"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="27"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -2670,12 +4122,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="26"/>
+      <c r="D5" s="24"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="27"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -2683,12 +4135,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="26"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="8"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="27"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -2696,12 +4148,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="26"/>
+      <c r="D7" s="24"/>
       <c r="E7" s="8"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="27"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="24"/>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -2709,12 +4161,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="26"/>
+      <c r="D8" s="24"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="27"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="24"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -2722,12 +4174,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="26"/>
+      <c r="D9" s="24"/>
       <c r="E9" s="8"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="27"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="24"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -2735,12 +4187,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="26"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="8"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="27"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="24"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -2748,12 +4200,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="26"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="8"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="27"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="24"/>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -2761,12 +4213,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="26"/>
+      <c r="D12" s="24"/>
       <c r="E12" s="8"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="27"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="24"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -2774,12 +4226,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="26"/>
+      <c r="D13" s="24"/>
       <c r="E13" s="8"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="27"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="24"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -2787,12 +4239,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="26"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="8"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="27"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="24"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -2800,23 +4252,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="26"/>
+      <c r="D15" s="24"/>
       <c r="E15" s="8"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="27"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="24"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="26"/>
+      <c r="D16" s="24"/>
       <c r="E16" s="8"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="27"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="24"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -2827,7 +4279,7 @@
       <c r="F17" s="11"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="24"/>
+      <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -2838,7 +4290,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="24"/>
+      <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -2849,7 +4301,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -2860,7 +4312,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -3279,63 +4731,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
       <c r="G3" s="19"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="33"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
       <c r="G4" s="19"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
       <c r="G5" s="19"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="29"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -3862,7 +5314,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -3874,232 +5326,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="24"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="24"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="24"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="24"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="24"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="24"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="24"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="24"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="24"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="24"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="24"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="24"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="24"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="24"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="24"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="24"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="29"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="27"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4108,9 +5560,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="29"/>
+      <c r="G20" s="27"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4119,9 +5571,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="29"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="24"/>
+      <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -4130,9 +5582,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="29"/>
+      <c r="G22" s="27"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="24"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -4141,9 +5593,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="29"/>
+      <c r="G23" s="27"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="24"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -4152,9 +5604,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="29"/>
+      <c r="G24" s="27"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="24"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -4165,7 +5617,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="24"/>
+      <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -4176,7 +5628,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="24"/>
+      <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -4187,7 +5639,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="24"/>
+      <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -4198,7 +5650,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="24"/>
+      <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -4209,7 +5661,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="24"/>
+      <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -4220,7 +5672,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="24"/>
+      <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -4231,7 +5683,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="24"/>
+      <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -4242,7 +5694,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="24"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -4253,7 +5705,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="24"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -4264,7 +5716,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="24"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -4275,7 +5727,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="24"/>
+      <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -4565,494 +6017,494 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="41"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="44"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="43"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="41"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="44"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="43"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="41"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="44"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="42"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="44"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="42"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="43"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="44"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="42"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="44"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="42"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="43"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="41"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="44"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="42"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="43"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="41"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="44"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="42"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="43"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="41"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="44"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="42"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="43"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="41"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="44"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="42"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="43"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="41"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="44"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="42"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="43"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="41"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="44"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="43"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="41"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="44"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="42"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="43"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="41"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="44"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="42"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="43"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="41"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="44"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="42"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="43"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="41"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="44"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="42"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="43"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="41"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="44"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="42"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="43"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="41"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="44"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="42"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="43"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="41"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="44"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="43"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="41"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="44"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="43"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="41"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="44"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="43"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="41"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="44"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="43"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="41"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="44"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="42"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="43"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="41"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="44"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="42"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="43"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="41"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="44"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="42"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="43"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="41"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="44"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="42"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="43"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="41"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="44"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="42"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="43"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="41"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="44"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="43"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="41"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
+      <c r="G30" s="40"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="I30" s="42"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="43"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
+      <c r="G31" s="40"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="I31" s="42"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="43"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="41"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
+      <c r="G32" s="40"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
+      <c r="I32" s="42"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="43"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="41"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="42"/>
+      <c r="G33" s="40"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="44"/>
+      <c r="I33" s="42"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="43"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="41"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="42"/>
+      <c r="G34" s="40"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="44"/>
+      <c r="I34" s="42"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="43"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="41"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="42"/>
+      <c r="G35" s="40"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="44"/>
+      <c r="I35" s="42"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="43"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="41"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
+      <c r="G36" s="40"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="44"/>
+      <c r="I36" s="42"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="43"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="41"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="42"/>
+      <c r="G37" s="40"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="44"/>
+      <c r="I37" s="42"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="43"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="41"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="42"/>
+      <c r="G38" s="40"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="44"/>
+      <c r="I38" s="42"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="43"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="41"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="42"/>
+      <c r="G39" s="40"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="44"/>
+      <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="43"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="41"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="42"/>
+      <c r="G40" s="40"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="44"/>
+      <c r="I40" s="42"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="43"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="41"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="42"/>
+      <c r="G41" s="40"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="44"/>
+      <c r="I41" s="42"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="43"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="41"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="42"/>
+      <c r="G42" s="40"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="44"/>
+      <c r="I42" s="42"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="6"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="17"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="42"/>
+      <c r="G43" s="40"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
@@ -5087,6 +6539,49 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-531148</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-531148</Url>
+      <Description>QAFFA7D2F2TC-2102087286-531148</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5464,7 +6959,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -5514,7 +7009,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5523,61 +7018,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-531148</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-531148</Url>
-      <Description>QAFFA7D2F2TC-2102087286-531148</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D6986EB-BB58-4D50-AC35-394136E3DEB9}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>